--- a/academias/Ciencias Sociales - Estadisticos 20211.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20211.xlsx
@@ -522,13 +522,13 @@
         <v>26.92</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7.69</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -545,25 +545,25 @@
         <v>23</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>4.35</v>
       </c>
       <c r="I3">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>8.699999999999999</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -615,25 +615,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G5">
-        <v>78.13</v>
+        <v>81.25</v>
       </c>
       <c r="H5">
-        <v>21.88</v>
+        <v>18.75</v>
       </c>
       <c r="I5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -650,25 +650,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>63.16</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H6">
-        <v>36.84</v>
+        <v>34.21</v>
       </c>
       <c r="I6">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>23.68</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -685,25 +685,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7">
-        <v>72.22</v>
+        <v>75</v>
       </c>
       <c r="H7">
-        <v>27.78</v>
+        <v>25</v>
       </c>
       <c r="I7">
         <v>7.8</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>16.67</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -755,25 +755,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H9">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
       <c r="I9">
         <v>10</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -790,25 +790,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>65.79000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H10">
-        <v>34.21</v>
+        <v>13.16</v>
       </c>
       <c r="I10">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
       <c r="J10">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>34.21</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -825,25 +825,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>59.38</v>
+        <v>84.38</v>
       </c>
       <c r="H11">
-        <v>40.63</v>
+        <v>15.63</v>
       </c>
       <c r="I11">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="J11">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>40.63</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -860,25 +860,25 @@
         <v>22</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>50</v>
+        <v>77.27</v>
       </c>
       <c r="H12">
-        <v>50</v>
+        <v>22.73</v>
       </c>
       <c r="I12">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>50</v>
+        <v>22.73</v>
       </c>
     </row>
   </sheetData>
@@ -944,22 +944,25 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80.77</v>
       </c>
       <c r="H2">
-        <v>100</v>
+        <v>19.23</v>
+      </c>
+      <c r="I2">
+        <v>6.7</v>
       </c>
       <c r="J2">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -976,22 +979,25 @@
         <v>23</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>100</v>
+        <v>4.35</v>
+      </c>
+      <c r="I3">
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1008,22 +1014,25 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
-        <v>100</v>
+        <v>2.94</v>
+      </c>
+      <c r="I4">
+        <v>8.5</v>
       </c>
       <c r="J4">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1040,22 +1049,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H5">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I5">
+        <v>7.2</v>
       </c>
       <c r="J5">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1072,22 +1084,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>60.53</v>
       </c>
       <c r="H6">
-        <v>100</v>
+        <v>39.47</v>
+      </c>
+      <c r="I6">
+        <v>7.8</v>
       </c>
       <c r="J6">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1104,22 +1119,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>77.78</v>
       </c>
       <c r="H7">
-        <v>100</v>
+        <v>22.22</v>
+      </c>
+      <c r="I7">
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1136,22 +1154,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="H8">
-        <v>100</v>
+        <v>51.52</v>
+      </c>
+      <c r="I8">
+        <v>8.300000000000001</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1168,22 +1189,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F9">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="H9">
-        <v>100</v>
+        <v>25.71</v>
+      </c>
+      <c r="I9">
+        <v>9.199999999999999</v>
       </c>
       <c r="J9">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1200,22 +1224,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H10">
-        <v>100</v>
+        <v>15.79</v>
+      </c>
+      <c r="I10">
+        <v>8.699999999999999</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1232,22 +1259,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>84.38</v>
       </c>
       <c r="H11">
-        <v>100</v>
+        <v>15.63</v>
+      </c>
+      <c r="I11">
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1264,22 +1294,25 @@
         <v>22</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F12">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="H12">
-        <v>100</v>
+        <v>36.36</v>
+      </c>
+      <c r="I12">
+        <v>7.1</v>
       </c>
       <c r="J12">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>36.36</v>
       </c>
     </row>
   </sheetData>
@@ -1345,25 +1378,25 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>73.08</v>
+        <v>80.77</v>
       </c>
       <c r="H2">
-        <v>26.92</v>
+        <v>19.23</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="J2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K2">
-        <v>7.69</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1380,25 +1413,25 @@
         <v>23</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>91.3</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H3">
+        <v>4.35</v>
+      </c>
+      <c r="I3">
         <v>8.699999999999999</v>
       </c>
-      <c r="I3">
-        <v>8.5</v>
-      </c>
       <c r="J3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>8.699999999999999</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1415,19 +1448,19 @@
         <v>34</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4">
-        <v>94.12</v>
+        <v>97.06</v>
       </c>
       <c r="H4">
-        <v>5.88</v>
+        <v>2.94</v>
       </c>
       <c r="I4">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -1450,25 +1483,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G5">
-        <v>78.13</v>
+        <v>90.63</v>
       </c>
       <c r="H5">
-        <v>21.88</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="I5">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K5">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1497,13 +1530,13 @@
         <v>36.84</v>
       </c>
       <c r="I6">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K6">
-        <v>23.68</v>
+        <v>21.05</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1520,25 +1553,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>72.22</v>
+        <v>77.78</v>
       </c>
       <c r="H7">
-        <v>27.78</v>
+        <v>22.22</v>
       </c>
       <c r="I7">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K7">
-        <v>16.67</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1567,7 +1600,7 @@
         <v>39.39</v>
       </c>
       <c r="I8">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="J8">
         <v>13</v>
@@ -1590,25 +1623,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H9">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
       <c r="I9">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="J9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K9">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1625,25 +1658,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>65.79000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H10">
-        <v>34.21</v>
+        <v>13.16</v>
       </c>
       <c r="I10">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>34.21</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1660,25 +1693,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G11">
-        <v>59.38</v>
+        <v>84.38</v>
       </c>
       <c r="H11">
-        <v>40.63</v>
+        <v>15.63</v>
       </c>
       <c r="I11">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K11">
-        <v>40.63</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1695,25 +1728,25 @@
         <v>22</v>
       </c>
       <c r="E12">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F12">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G12">
-        <v>50</v>
+        <v>77.27</v>
       </c>
       <c r="H12">
-        <v>50</v>
+        <v>22.73</v>
       </c>
       <c r="I12">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="K12">
-        <v>50</v>
+        <v>22.73</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Ciencias Sociales - Estadisticos 20211.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20211.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="1er Parcial" sheetId="1" r:id="rId1"/>
     <sheet name="2o Parcial" sheetId="2" r:id="rId2"/>
-    <sheet name="3er Parcial" sheetId="3" r:id="rId3"/>
+    <sheet name="Final" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -103,6 +103,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -155,8 +159,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -457,42 +463,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -515,19 +524,19 @@
       <c r="F2">
         <v>7</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>73.08</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>26.92</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>6.5</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>3.85</v>
       </c>
     </row>
@@ -550,19 +559,19 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>95.65000000000001</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>4.35</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.4</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>4.35</v>
       </c>
     </row>
@@ -585,19 +594,19 @@
       <c r="F4">
         <v>2</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>94.12</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>5.88</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>8.9</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>2.94</v>
       </c>
     </row>
@@ -620,19 +629,19 @@
       <c r="F5">
         <v>6</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>81.25</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>18.75</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.5</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>6.25</v>
       </c>
     </row>
@@ -655,19 +664,19 @@
       <c r="F6">
         <v>13</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>65.79000000000001</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>34.21</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>8</v>
       </c>
       <c r="J6">
         <v>8</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>21.05</v>
       </c>
     </row>
@@ -690,19 +699,19 @@
       <c r="F7">
         <v>9</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>75</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>25</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.8</v>
       </c>
       <c r="J7">
         <v>5</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>13.89</v>
       </c>
     </row>
@@ -725,19 +734,19 @@
       <c r="F8">
         <v>13</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>60.61</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>39.39</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J8">
         <v>13</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>39.39</v>
       </c>
     </row>
@@ -760,19 +769,19 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>88.56999999999999</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>11.43</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>10</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>11.43</v>
       </c>
     </row>
@@ -795,19 +804,19 @@
       <c r="F10">
         <v>5</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>86.84</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>13.16</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8.4</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>13.16</v>
       </c>
     </row>
@@ -830,19 +839,19 @@
       <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>84.38</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>15.63</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>7.5</v>
       </c>
       <c r="J11">
         <v>5</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>15.63</v>
       </c>
     </row>
@@ -865,19 +874,19 @@
       <c r="F12">
         <v>5</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>77.27</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>22.73</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7.2</v>
       </c>
       <c r="J12">
         <v>5</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>22.73</v>
       </c>
     </row>
@@ -891,42 +900,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -949,19 +961,19 @@
       <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>80.77</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>19.23</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>6.7</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>3.85</v>
       </c>
     </row>
@@ -984,19 +996,19 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>95.65000000000001</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>4.35</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>4.35</v>
       </c>
     </row>
@@ -1019,19 +1031,19 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>97.06</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>2.94</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>8.5</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>2.94</v>
       </c>
     </row>
@@ -1054,19 +1066,19 @@
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>90.63</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>9.380000000000001</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.2</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>6.25</v>
       </c>
     </row>
@@ -1089,19 +1101,19 @@
       <c r="F6">
         <v>15</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>60.53</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>39.47</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.8</v>
       </c>
       <c r="J6">
         <v>10</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>26.32</v>
       </c>
     </row>
@@ -1124,19 +1136,19 @@
       <c r="F7">
         <v>8</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>77.78</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>22.22</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.8</v>
       </c>
       <c r="J7">
         <v>6</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>16.67</v>
       </c>
     </row>
@@ -1159,19 +1171,19 @@
       <c r="F8">
         <v>17</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>48.48</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>51.52</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.300000000000001</v>
       </c>
       <c r="J8">
         <v>17</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>51.52</v>
       </c>
     </row>
@@ -1194,19 +1206,19 @@
       <c r="F9">
         <v>9</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>74.29000000000001</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>25.71</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>9.199999999999999</v>
       </c>
       <c r="J9">
         <v>9</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>25.71</v>
       </c>
     </row>
@@ -1229,19 +1241,19 @@
       <c r="F10">
         <v>6</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>84.20999999999999</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>15.79</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J10">
         <v>6</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>15.79</v>
       </c>
     </row>
@@ -1264,19 +1276,19 @@
       <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>84.38</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>15.63</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>5</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>15.63</v>
       </c>
     </row>
@@ -1299,19 +1311,19 @@
       <c r="F12">
         <v>8</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>63.64</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>36.36</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7.1</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>36.36</v>
       </c>
     </row>
@@ -1325,42 +1337,45 @@
   <dimension ref="A1:K12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
+    <col min="1" max="1" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="7" max="8" width="9.140625" style="1"/>
+    <col min="9" max="9" width="9.140625" style="2"/>
+    <col min="11" max="11" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1383,19 +1398,19 @@
       <c r="F2">
         <v>5</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="1">
         <v>80.77</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
         <v>19.23</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>6.7</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <v>3.85</v>
       </c>
     </row>
@@ -1418,19 +1433,19 @@
       <c r="F3">
         <v>1</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="1">
         <v>95.65000000000001</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
         <v>4.35</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>8.699999999999999</v>
       </c>
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <v>4.35</v>
       </c>
     </row>
@@ -1453,19 +1468,19 @@
       <c r="F4">
         <v>1</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="1">
         <v>97.06</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="1">
         <v>2.94</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <v>2.94</v>
       </c>
     </row>
@@ -1488,19 +1503,19 @@
       <c r="F5">
         <v>3</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="1">
         <v>90.63</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="1">
         <v>9.380000000000001</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>7.5</v>
       </c>
       <c r="J5">
         <v>2</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <v>6.25</v>
       </c>
     </row>
@@ -1523,19 +1538,19 @@
       <c r="F6">
         <v>14</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="1">
         <v>63.16</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="1">
         <v>36.84</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>7.9</v>
       </c>
       <c r="J6">
         <v>8</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="1">
         <v>21.05</v>
       </c>
     </row>
@@ -1558,19 +1573,19 @@
       <c r="F7">
         <v>8</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>77.78</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
         <v>22.22</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>7.9</v>
       </c>
       <c r="J7">
         <v>5</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>13.89</v>
       </c>
     </row>
@@ -1593,19 +1608,19 @@
       <c r="F8">
         <v>13</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="1">
         <v>60.61</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
         <v>39.39</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>8.4</v>
       </c>
       <c r="J8">
         <v>13</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="1">
         <v>39.39</v>
       </c>
     </row>
@@ -1628,19 +1643,19 @@
       <c r="F9">
         <v>4</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="1">
         <v>88.56999999999999</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>11.43</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>9.9</v>
       </c>
       <c r="J9">
         <v>4</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="1">
         <v>11.43</v>
       </c>
     </row>
@@ -1663,19 +1678,19 @@
       <c r="F10">
         <v>5</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="1">
         <v>86.84</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
         <v>13.16</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>8.6</v>
       </c>
       <c r="J10">
         <v>5</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="1">
         <v>13.16</v>
       </c>
     </row>
@@ -1698,19 +1713,19 @@
       <c r="F11">
         <v>5</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="1">
         <v>84.38</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="1">
         <v>15.63</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>8</v>
       </c>
       <c r="J11">
         <v>5</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="1">
         <v>15.63</v>
       </c>
     </row>
@@ -1733,19 +1748,19 @@
       <c r="F12">
         <v>5</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="1">
         <v>77.27</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="1">
         <v>22.73</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>7.4</v>
       </c>
       <c r="J12">
         <v>5</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="1">
         <v>22.73</v>
       </c>
     </row>

--- a/academias/Ciencias Sociales - Estadisticos 20211.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20211.xlsx
@@ -104,7 +104,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="2">

--- a/academias/Ciencias Sociales - Estadisticos 20211.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20211.xlsx
@@ -1201,25 +1201,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
-        <v>74.29000000000001</v>
+        <v>77.14</v>
       </c>
       <c r="H9" s="1">
-        <v>25.71</v>
+        <v>22.86</v>
       </c>
       <c r="I9" s="2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="J9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K9" s="1">
-        <v>25.71</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1650,7 +1650,7 @@
         <v>11.43</v>
       </c>
       <c r="I9" s="2">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J9">
         <v>4</v>

--- a/academias/Ciencias Sociales - Estadisticos 20211.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20211.xlsx
@@ -659,25 +659,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" s="1">
-        <v>65.79000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="H6" s="1">
-        <v>34.21</v>
+        <v>31.58</v>
       </c>
       <c r="I6" s="2">
         <v>8</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K6" s="1">
-        <v>21.05</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1533,25 +1533,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" s="1">
-        <v>63.16</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>36.84</v>
+        <v>34.21</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K6" s="1">
-        <v>21.05</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="7" spans="1:11">

--- a/academias/Ciencias Sociales - Estadisticos 20211.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20211.xlsx
@@ -706,13 +706,13 @@
         <v>25</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
-        <v>13.89</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1580,13 +1580,13 @@
         <v>22.22</v>
       </c>
       <c r="I7" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K7" s="1">
-        <v>13.89</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="8" spans="1:11">

--- a/academias/Ciencias Sociales - Estadisticos 20211.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20211.xlsx
@@ -534,10 +534,10 @@
         <v>6.5</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -566,13 +566,13 @@
         <v>4.35</v>
       </c>
       <c r="I3" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -601,13 +601,13 @@
         <v>5.88</v>
       </c>
       <c r="I4" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -624,25 +624,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="1">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="H5" s="1">
-        <v>18.75</v>
+        <v>15.63</v>
       </c>
       <c r="I5" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -671,13 +671,13 @@
         <v>31.58</v>
       </c>
       <c r="I6" s="2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>18.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -694,25 +694,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="H7" s="1">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="I7" s="2">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -729,25 +729,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>60.61</v>
+        <v>63.64</v>
       </c>
       <c r="H8" s="1">
-        <v>39.39</v>
+        <v>36.36</v>
       </c>
       <c r="I8" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -764,25 +764,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1">
-        <v>11.43</v>
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>11.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -799,25 +799,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="1">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H10" s="1">
-        <v>13.16</v>
+        <v>10.53</v>
       </c>
       <c r="I10" s="2">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>13.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -846,13 +846,13 @@
         <v>15.63</v>
       </c>
       <c r="I11" s="2">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -869,25 +869,25 @@
         <v>22</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>77.27</v>
+        <v>86.36</v>
       </c>
       <c r="H12" s="1">
-        <v>22.73</v>
+        <v>13.64</v>
       </c>
       <c r="I12" s="2">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -971,10 +971,10 @@
         <v>6.7</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1003,13 +1003,13 @@
         <v>4.35</v>
       </c>
       <c r="I3" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1038,13 +1038,13 @@
         <v>2.94</v>
       </c>
       <c r="I4" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1061,25 +1061,25 @@
         <v>32</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="1">
-        <v>90.63</v>
+        <v>93.75</v>
       </c>
       <c r="H5" s="1">
-        <v>9.380000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="I5" s="2">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1108,13 +1108,13 @@
         <v>39.47</v>
       </c>
       <c r="I6" s="2">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1131,25 +1131,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>77.78</v>
+        <v>80.56</v>
       </c>
       <c r="H7" s="1">
-        <v>22.22</v>
+        <v>19.44</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
       <c r="J7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>16.67</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1166,25 +1166,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F8">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G8" s="1">
-        <v>48.48</v>
+        <v>60.61</v>
       </c>
       <c r="H8" s="1">
-        <v>51.52</v>
+        <v>39.39</v>
       </c>
       <c r="I8" s="2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J8">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>51.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1201,25 +1201,25 @@
         <v>35</v>
       </c>
       <c r="E9">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G9" s="1">
-        <v>77.14</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H9" s="1">
-        <v>22.86</v>
+        <v>11.43</v>
       </c>
       <c r="I9" s="2">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="J9">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>22.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1236,25 +1236,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>84.20999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="H10" s="1">
-        <v>15.79</v>
+        <v>13.16</v>
       </c>
       <c r="I10" s="2">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1283,13 +1283,13 @@
         <v>15.63</v>
       </c>
       <c r="I11" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1306,25 +1306,25 @@
         <v>22</v>
       </c>
       <c r="E12">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>63.64</v>
+        <v>86.36</v>
       </c>
       <c r="H12" s="1">
-        <v>36.36</v>
+        <v>13.64</v>
       </c>
       <c r="I12" s="2">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="J12">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>36.36</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1393,25 +1393,25 @@
         <v>26</v>
       </c>
       <c r="E2">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>80.77</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H2" s="1">
-        <v>19.23</v>
+        <v>3.85</v>
       </c>
       <c r="I2" s="2">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1440,13 +1440,13 @@
         <v>4.35</v>
       </c>
       <c r="I3" s="2">
-        <v>8.699999999999999</v>
+        <v>8</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>4.35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1475,13 +1475,13 @@
         <v>2.94</v>
       </c>
       <c r="I4" s="2">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>2.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1510,13 +1510,13 @@
         <v>9.380000000000001</v>
       </c>
       <c r="I5" s="2">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1533,25 +1533,25 @@
         <v>38</v>
       </c>
       <c r="E6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G6" s="1">
-        <v>65.79000000000001</v>
+        <v>60.53</v>
       </c>
       <c r="H6" s="1">
-        <v>34.21</v>
+        <v>39.47</v>
       </c>
       <c r="I6" s="2">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>18.42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1568,25 +1568,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>77.78</v>
+        <v>80.56</v>
       </c>
       <c r="H7" s="1">
-        <v>22.22</v>
+        <v>19.44</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.1</v>
       </c>
       <c r="J7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>11.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1615,13 +1615,13 @@
         <v>39.39</v>
       </c>
       <c r="I8" s="2">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="J8">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>39.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1650,13 +1650,13 @@
         <v>11.43</v>
       </c>
       <c r="I9" s="2">
-        <v>9.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>11.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1685,13 +1685,13 @@
         <v>13.16</v>
       </c>
       <c r="I10" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J10">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>13.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1708,25 +1708,25 @@
         <v>32</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H11" s="1">
-        <v>15.63</v>
+        <v>12.5</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>15.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1743,25 +1743,25 @@
         <v>22</v>
       </c>
       <c r="E12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>77.27</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>22.73</v>
+        <v>18.18</v>
       </c>
       <c r="I12" s="2">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>22.73</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Ciencias Sociales - Estadisticos 20211.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20211.xlsx
@@ -1131,25 +1131,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" s="1">
-        <v>80.56</v>
+        <v>83.33</v>
       </c>
       <c r="H7" s="1">
-        <v>19.44</v>
+        <v>16.67</v>
       </c>
       <c r="I7" s="2">
         <v>7.5</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
